--- a/collections/test_script.xlsx
+++ b/collections/test_script.xlsx
@@ -34,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +42,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,8 +614,8 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-094853-WXZGIP
-ktp: 6621997483706595
+          <t xml:space="preserve">nomor_transaksi: AKS-20260824-101719-SHWAVL
+ktp: 6165647564759970
 </t>
         </is>
       </c>
@@ -629,7 +638,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
     </row>
@@ -2694,10 +2703,9 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-093407-SRVUEE
-ktp: 3404387391812951
-nomor_loan: LN-382229
-nomor_loan: LN-035643
+          <t xml:space="preserve">nomor_transaksi: AKS-20260902-161803-BXXUXZ
+ktp: 4604279465860287
+nomor_loan: LN-976237
 </t>
         </is>
       </c>
@@ -2710,7 +2718,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2720,7 +2728,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -2767,9 +2775,9 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260814-155028-BXHGYD
-ktp: 7930920405925650
-nomor_loan: LN-383173
+          <t xml:space="preserve">nomor_transaksi: AKS-20260902-145009-WHOOQD
+ktp: 6447939634195919
+nomor_loan: LN-725452
 </t>
         </is>
       </c>
@@ -2792,7 +2800,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
     </row>
@@ -3190,8 +3198,8 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260814-140623-SLFSGB
-ktp: 3168900258421529
+          <t xml:space="preserve">nomor_transaksi: AKS-20260820-155153-PZOEXN
+ktp: 1305984111740260
 </t>
         </is>
       </c>
@@ -3214,7 +3222,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -3261,8 +3269,8 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260814-140832-KVISKL
-ktp: 7360359479212527
+          <t xml:space="preserve">nomor_transaksi: AKS-20260820-155401-TABFQH
+ktp: 0928839527027039
 </t>
         </is>
       </c>
@@ -3285,7 +3293,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3340,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">ktp: 5144664616295173
+          <t xml:space="preserve">ktp: 7046120439275291
 </t>
         </is>
       </c>
@@ -3355,7 +3363,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3410,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">ktp: 8840920497274831
+          <t xml:space="preserve">ktp: 4341979488740436
 </t>
         </is>
       </c>
@@ -3425,7 +3433,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>
@@ -3472,8 +3480,8 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260814-140846-BXWLLZ
-ktp: 4929626691647152
+          <t xml:space="preserve">nomor_transaksi: AKS-20260820-155416-JNUTVO
+ktp: 8777671845561086
 </t>
         </is>
       </c>
@@ -3496,7 +3504,300 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Akseptasi H2H</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Submit Draft Multi Fasilitas</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TC-42</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Multi Fasilitas &gt; 2 Pengajuan (Limit Berjenjang berdasar Outstanding)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Simulasi 4 pengajuan berturut-turut pada 1 KTP hingga tahap Inquiry Loan</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1. Pengajuan 1: Submit (UP 300jt) -&gt; Inquiry (Out: 200jt)
+2. Pengajuan 2: Submit (UP 200jt) -&gt; Inquiry (Out: 200jt)
+3. Pengajuan 3: Submit (UP 100jt) -&gt; Inquiry (Out: 50jt)
+4. Pengajuan 4: Submit (UP 100jt) -&gt; Ditolak (Limit Akumulasi &gt; 500jt)
+5. Validasi DB Tabel Limit Akumulasi</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260820-155605-IMZMWW
+ktp: 7908190488617109
+nomor_loan: LN-086688
+nomor_transaksi: AKS-20260820-155605-PYVNNE
+nomor_loan: LN-744052
+nomor_transaksi: AKS-20260820-155606-ZMKZBD
+nomor_loan: LN-009170
+nomor_transaksi: AKS-20260820-155606-LPJWHG
+</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1. Sistem menolak pengajuan Submit Draft ke-4 karena limit akumulasi (Outstanding lama + UP Baru) &gt; 500 Juta
+2. Data tidak terecord atau termutasi di Database.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Akseptasi H2H</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Submit Draft Multi Fasilitas</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TC-43</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Multi Fasilitas &gt; 2 Pengajuan Sampai Payment (Limit Berjenjang berdasar Outstanding)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Simulasi 4 pengajuan berturut-turut pada 1 KTP hingga tahap Payment</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1. Pengajuan 1: Submit (UP 300jt) -&gt; Inquiry -&gt; Otorisasi -&gt; Payment (Polis Terbit)
+2. Pengajuan 2: Submit (UP 200jt) -&gt; Inquiry -&gt; Otorisasi -&gt; Payment (Polis Terbit)
+3. Pengajuan 3: Submit (UP 100jt) -&gt; Inquiry -&gt; Otorisasi -&gt; Payment (Polis Terbit)
+4. Pengajuan 4: Submit (UP 100jt) -&gt; Ditolak (Limit Akumulasi &gt; 500jt)
+5. Validasi DB Tabel Limit Akumulasi &amp; Pengecekan ACS, FMS</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260820-155606-KYTATP
+ktp: 6382463712445182
+nomor_loan: LN-037196
+nomor_transaksi: AKS-20260820-155801-REIUHP
+nomor_loan: LN-577490
+nomor_transaksi: AKS-20260820-155957-DVEWWH
+nomor_loan: LN-674157
+nomor_transaksi: AKS-20260820-160155-MUCZXF
+</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1. Sistem menolak pengajuan Submit Draft ke-4 karena limit akumulasi (Outstanding lama + UP Baru) &gt; 500 Juta
+2. Data tidak terecord atau termutasi di Database.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Akseptasi H2H</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Submit Draft Multi Fasilitas</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TC-44</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Multi Fasilitas Batal (Reset Kalkulasi)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Simulasi pengajuan berturut-turut pada 1 KTP hingga tahap Inquiry Loan, lalu batalkan salah satu, dan ajukan lagi untuk memastikan kalkulasi reset</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>1. Pengajuan 1: Submit (UP 300jt) -&gt; Inquiry (Out: 200jt)
+2. Pengajuan 2: Submit (UP 200jt) -&gt; Inquiry (Out: 200jt)
+3. Pengajuan 3: Submit (UP 100jt) -&gt; Inquiry (Out: 50jt)
+4. Batal Pengajuan 3
+5. Pengajuan 4: Submit (UP 100jt) -&gt; Inquiry (Out: 100jt)
+6. Pengajuan 5: Submit (UP 50jt) -&gt; Ditolak (Limit Akumulasi &gt; 500jt)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260820-160155-CQTSOQ
+ktp: 9777963197043459
+nomor_loan: LN-330350
+nomor_transaksi: AKS-20260820-160155-KRYSMR
+nomor_loan: LN-376753
+nomor_transaksi: AKS-20260820-160156-VVXJZW
+nomor_loan: LN-300776
+nomor_transaksi: AKS-20260820-160156-QYCXYK
+nomor_loan: LN-379387
+nomor_transaksi: AKS-20260820-160156-UFWMIK
+</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1. Sistem menerima pengajuan setelah ada pembatalan, dan menolak pengajuan terakhir karena limit akumulasi (Outstanding lama + UP Baru) &gt; 500 Juta
+2. Data tidak terecord atau termutasi di Database.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Akseptasi H2H</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Submit Draft Multi Fasilitas</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TC-45</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Validasi Response Nilai Akumulasi Limit Multi Fasilitas</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>KTP belum memiliki fasilitas aktif. Hit menggunakan API Automation.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>1. Pengajuan 1: Submit Draft (UP 300 Juta) -&gt; Inquiry Loan (Outstanding 100 Juta)
+2. Pengajuan 2: Submit Draft (UP 100 Juta)
+3. Validasi field nilai_akumulasi pada Response API Pengajuan 2
+4. Menampilkan Tabel Validasi Response Nilai Akumulasi</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260820-160156-MWWBUF
+ktp: 9207441215116180
+nomor_loan: LN-875740
+nomor_transaksi: AKS-20260820-160157-THXRWK
+nomor_loan: LN-479646
+</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>1. Sistem memproses pengajuan 2 dengan sukses.
+2. Field nilai_akumulasi pada response sesuai dengan total akumulasi (Outstanding lama + UP Baru).
+3. Tabel validasi menampilkan hasil perbandingan yang sesuai.
+4. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>20/08/2026</t>
         </is>
       </c>
     </row>

--- a/collections/test_script.xlsx
+++ b/collections/test_script.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,32 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00008000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00003366"/>
+        <bgColor rgb="00003366"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -52,9 +71,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -422,189 +450,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Test Script - TESTING (TESTING)</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Unnamed: 1</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Unnamed: 2</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Unnamed: 3</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Unnamed: 4</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Unnamed: 5</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Unnamed: 6</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Unnamed: 7</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Unnamed: 8</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Unnamed: 9</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Unnamed: 10</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Unnamed: 11</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Unnamed: 12</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Unnamed: 13</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Test Script - PRJ-12345 Judul Laporan Project Baru</t>
         </is>
       </c>
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Nama Modul</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>TestCase-ID</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Jenis Test</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Pre Condition</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Nama Tester</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Tanggal Testing</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>TC-1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Validasi sukses kalkulasi premi dengan UP 5.000.000 (Premi Dasar &lt; Batas Meterai, Admin = Batas Bawah)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/draft/submit
@@ -612,71 +591,72 @@
 4. Hit Send dan check hasil response postman dan DB</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260824-101719-SHWAVL
-ktp: 6165647564759970
-</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260929-105707-NRNWSY
+ktp: 5766128129083275
+</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
         <is>
           <t>1. API berhasil memproses request (HTTP 200 OK).
 2. Field dinamis pada response (seperti nomor_transaksi, premi) ter-generate dengan format valid.
 3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>24/08/2026</t>
+      <c r="L4" s="1" t="n"/>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>TC-2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Submit pengajuan akseptasi dengan uang pertanggungan bernilai 0</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/draft/submit
@@ -684,140 +664,142 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-094855-RHYKMR
-ktp: 7061651407279214
-</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153105-ARZCIN
+ktp: 4216579806630659
+</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L5" s="1" t="n"/>
+      <c r="M5" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>TC-3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="1" t="inlineStr">
         <is>
           <t>Submit pengajuan akseptasi menggunakan kode bank yang tidak ada di sistem mapping</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/draft/submit dan Edit field kode_bank 
 3. Hit Send</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-094855-VVIKIN
-ktp: 3169545050669331
-</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153105-RFZEAP
+ktp: 9538277451891370
+</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L6" s="1" t="n"/>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>TC-4</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="1" t="inlineStr">
         <is>
           <t>Submit pengajuan akseptasi dengan code produk yang sesuai dengan product bank</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">[Test_Step-1] :  Buka Postman
 [Test_Step-2] :  {{TESTING_API_GATEWAY}}/akseptasi/draft/submit 
@@ -825,71 +807,72 @@
 </t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-094855-PKYKQL
-ktp: 0687495697403336
-</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153105-QAOQRT
+ktp: 0011556473242204
+</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
         <is>
           <t>1. API berhasil memproses request (HTTP 200 OK).
 2. Field dinamis pada response (seperti nomor_transaksi, premi) ter-generate dengan format valid.
 3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L7" s="1" t="n"/>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>A1 - Kalkulasi Premi</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>TC-5</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>Hit endpoint kalkulasi premi untuk mendapatkan nilai premi secara instan dengan parameter valid</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>Service API aktif dan database dalam keadaan normal.</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/calculate/premi
@@ -897,70 +880,71 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ktp: 3118541964223781
-</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ktp: 6505589433626507
+</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
         <is>
           <t>1. API berhasil memproses request (HTTP 200 OK).
 2. Field dinamis pada response (seperti nomor_transaksi, premi) ter-generate dengan format valid.
 3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L8" s="1" t="n"/>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>A4 - Inquiry Nomor Loan</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>TC-6</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>Inquiry data loan dengan menggunakan nomor transaksi draft akseptasi dan nomor rekening (loan) yang valid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>Terdapat data Draft Akseptasi yang telah sukses disubmit dan tercatat di database.</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/loan/inquiry
@@ -968,72 +952,73 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-094855-PKYKQL
-ktp: 0687495697403336
-nomor_loan: LN-441777
-</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153105-QAOQRT
+ktp: 0011556473242204
+nomor_loan: LN-330841
+</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
         <is>
           <t>1. API berhasil memproses request (HTTP 200 OK).
 2. Field dinamis pada response (seperti nomor_transaksi, premi) ter-generate dengan format valid.
 3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L9" s="1" t="n"/>
+      <c r="M9" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>A4 - Inquiry Nomor Loan</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>TC-7</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="1" t="inlineStr">
         <is>
           <t>Mencoba inquiry data loan menggunakan nomor_transaksi fiktif yang tidak ada di database</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>Terdapat data Draft Akseptasi yang telah sukses disubmit dan tercatat di database.</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/loan/inquiry
@@ -1041,72 +1026,73 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-094855-PKYKQL
-ktp: 0687495697403336
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153105-QAOQRT
+ktp: 0011556473242204
 nomor_transaksi: TRX-INVALID
-nomor_loan: LN-072135
-</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+nomor_loan: LN-180283
+</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L10" s="1" t="n"/>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>A5 - Otorisasi Penyelia Bank</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>TC-8</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Submit status otorisasi DISETUJUI dari penyelia bank </t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>Terdapat data Loan yang telah sukses melewati tahap Inquiry (A4).</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/loan/otorisasi
@@ -1114,72 +1100,73 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-094855-PKYKQL
-ktp: 0687495697403336
-nomor_loan: LN-441777
-</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153105-QAOQRT
+ktp: 0011556473242204
+nomor_loan: LN-330841
+</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>1. API berhasil memproses request (HTTP 200 OK).
 2. Field dinamis pada response (seperti nomor_transaksi, premi) ter-generate dengan format valid.
 3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L11" s="1" t="n"/>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>A5 - Otorisasi Penyelia Bank</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>TC-9</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="1" t="inlineStr">
         <is>
           <t>Submit status otorisasi DITOLAK karena nasabah batal kredit atau plafon final tidak disetujui</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>Terdapat data Loan yang telah sukses melewati tahap Inquiry (A4).</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/loan/otorisasi
@@ -1187,71 +1174,72 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-094855-PKYKQL
-ktp: 0687495697403336
-nomor_loan: LN-441777
-</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153105-QAOQRT
+ktp: 0011556473242204
+nomor_loan: LN-330841
+</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L12" s="1" t="n"/>
+      <c r="M12" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>A6 - Notifikasi Pembayaran Premi</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>TC-10</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="1" t="inlineStr">
         <is>
           <t>Submit notifikasi pembayaran premi dengan jumlah uang yang sama persis dengan total premi (Full Payment)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>Terdapat data pengajuan yang telah mendapatkan Otorisasi (A5) dengan status DISETUJUI.</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/loan/payment
@@ -1259,72 +1247,73 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-094920-KBWKJB
-ktp: 2928301182700269
-nomor_loan: LN-116216
-</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153127-ZGSABF
+ktp: 3068239285425980
+nomor_loan: LN-919101
+</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
         <is>
           <t>1. API berhasil memproses request (HTTP 200 OK).
 2. Field dinamis pada response (seperti nomor_transaksi, premi) ter-generate dengan format valid.
 3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L13" s="1" t="n"/>
+      <c r="M13" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>A6 - Notifikasi Pembayaran Premi</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>TC-11</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Submit notifikasi pembayaran premi dengan nominal yang kurang dari total tagihan premi </t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>Terdapat data pengajuan yang telah mendapatkan Otorisasi (A5) dengan status DISETUJUI.</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/loan/payment
@@ -1332,72 +1321,73 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-094858-UEQTGC
-ktp: 6913777406851537
-nomor_loan: LN-973526
-</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153106-QIQRMD
+ktp: 6231291102549549
+nomor_loan: LN-304518
+</t>
+        </is>
+      </c>
+      <c r="J14" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request karena nominal pembayaran salah.
 2. Response menampilkan pesan: 'Nominal Pembayaran tidak sesuai dengan Nominal Premi yang sebenarnya'.
 3. Data pembayaran tidak ter-record di Database.</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L14" s="1" t="n"/>
+      <c r="M14" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N14" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>A7 - Pembatalan Draft (Canceled)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="1" t="inlineStr">
         <is>
           <t>TC-12</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Submit permintaan pembatalan draf akseptasi sebelum premi dibayarkan</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>Terdapat data pengajuan aktif di database yang memenuhi syarat pembatalan.</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/draft/canceled
@@ -1405,73 +1395,74 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-094855-PKYKQL
-ktp: 0687495697403336
-nomor_loan: LN-441777
-nomor_transaksi: AKS-20260810-094853-WXZGIP
-</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260923-135731-JXQPXW
+ktp: 4767841473044524
+nomor_loan: LN-6658541626
+nomor_transaksi: TRX-MOCK
+</t>
+        </is>
+      </c>
+      <c r="J15" s="1" t="inlineStr">
         <is>
           <t>1. API berhasil memproses request (HTTP 200 OK).
 2. Field dinamis pada response (seperti nomor_transaksi, premi) ter-generate dengan format valid.
 3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="K15" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="L15" s="1" t="n"/>
+      <c r="M15" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N15" s="1" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>A7 - Pembatalan Draft (Canceled)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="1" t="inlineStr">
         <is>
           <t>TC-13</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="1" t="inlineStr">
         <is>
           <t>melakukan pembatalan (A7) pada nomor transaksi yang statusnya sudah POLIS_ISSUED/Terbit</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>Terdapat data pengajuan aktif di database yang memenuhi syarat pembatalan.</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/draft/canceled
@@ -1479,71 +1470,72 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-095125-CCBTFA
-ktp: 2640414536169631
-nomor_loan: LN-538320
-</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153339-VKXGSQ
+ktp: 3409172084303968
+nomor_loan: LN-760958
+</t>
+        </is>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L16" s="1" t="n"/>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N16" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>A7 - Pembatalan Draft (Canceled)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="1" t="inlineStr">
         <is>
           <t>TC-14</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="1" t="inlineStr">
         <is>
           <t>Mencoba melakukan pembatalan dengan menggunakan nomor transaksi yang tidak terdaftar</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>Terdapat data pengajuan aktif di database yang memenuhi syarat pembatalan.</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/draft/canceled
@@ -1551,72 +1543,73 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-094855-PKYKQL
-ktp: 0687495697403336
-nomor_loan: LN-441777
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153105-QAOQRT
+ktp: 0011556473242204
+nomor_loan: LN-330841
 nomor_transaksi: TRX-INVALID
 </t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L17" s="1" t="n"/>
+      <c r="M17" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N17" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="1" t="inlineStr">
         <is>
           <t>TC-15</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="1" t="inlineStr">
         <is>
           <t>Submit pengajuan akseptasi dengan parameter 'usia' yang tidak cocok dengan hasil perhitungan 'tanggal_lahir'</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/draft/submit
@@ -1624,70 +1617,71 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-095136-TSWFWH
-ktp: 8543131055449504
-</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153345-BFCDLK
+ktp: 8206789529517435
+</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L18" s="1" t="n"/>
+      <c r="M18" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N18" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="1" t="inlineStr">
         <is>
           <t>TC-16</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="1" t="inlineStr">
         <is>
           <t>Submit pengajuan dengan 'tenor' yang tidak sesuai dengan jarak antara 'tanggal_rencana_realisasi' dan 'tanggal_akhir_asuransi'</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/draft/submit
@@ -1695,70 +1689,71 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-095136-YZBRWO
-ktp: 0240573155028148
-</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153345-URDLNK
+ktp: 7948493240666194
+</t>
+        </is>
+      </c>
+      <c r="J19" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L19" s="1" t="n"/>
+      <c r="M19" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N19" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="1" t="inlineStr">
         <is>
           <t>TC-17</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="1" t="inlineStr">
         <is>
           <t>Submit pengajuan dengan 'kode_pos' berformat salah (mengandung huruf) atau kode fiktif yang tidak terdaftar di database</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/draft/submit
@@ -1766,70 +1761,71 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-095136-IHKIZS
-ktp: 8488796958635494
-</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153345-IAOGKW
+ktp: 6457290561975017
+</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L20" s="1" t="n"/>
+      <c r="M20" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N20" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="1" t="inlineStr">
         <is>
           <t>TC-18</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="1" t="inlineStr">
         <is>
           <t>Submit pengajuan dimana Usia ditambah Tenor Pinjaman melebihi batas usia maksimal pertanggungan asuransi</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/draft/submit
@@ -1837,70 +1833,71 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-095136-EPSIPR
-ktp: 7883901891480519
-</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260921-084945-ALYJKP
+ktp: 1314437289480146
+</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="K21" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="L21" s="1" t="n"/>
+      <c r="M21" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N21" s="1" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="1" t="inlineStr">
         <is>
           <t>TC-19</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="1" t="inlineStr">
         <is>
           <t>Submit pengajuan dengan tanggal_rencana_realisasi lebih kecil dari tanggal hari ini (Backdated)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/draft/submit
@@ -1908,70 +1905,71 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-095136-AOVQLY
-ktp: 2656511007919077
-</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153345-ZAGCKQ
+ktp: 1249079084266919
+</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L22" s="1" t="n"/>
+      <c r="M22" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N22" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="1" t="inlineStr">
         <is>
           <t>TC-20</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="1" t="inlineStr">
         <is>
           <t>Submit pengajuan akseptasi menggunakan kode cabang bank atau kode unit kerja yang fiktif atau tidak terdaftar</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/draft/submit
@@ -1979,71 +1977,72 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-095136-HNGUKI
-ktp: 4288329925398444
-</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153345-VAUMAY
+ktp: 7016146106710045
+</t>
+        </is>
+      </c>
+      <c r="J23" s="1" t="inlineStr">
         <is>
           <t>1. API berhasil memproses request (HTTP 200 OK).
 2. Field dinamis pada response (seperti nomor_transaksi, premi) ter-generate dengan format valid.
 3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L23" s="1" t="n"/>
+      <c r="M23" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N23" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>TC-21</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="1" t="inlineStr">
         <is>
           <t>Check semua Mandatory Field</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {base_url}/akseptasi/draft/submit
@@ -2052,69 +2051,70 @@
 5. Hit Send</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-095157-FDVATC
-</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260923-140001-JWTQSO
+</t>
+        </is>
+      </c>
+      <c r="J24" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L24" s="1" t="n"/>
+      <c r="M24" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N24" s="1" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>A4 - Inquiry Nomor Loan</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="1" t="inlineStr">
         <is>
           <t>TC-22</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="1" t="inlineStr">
         <is>
           <t>Hit inquiry loan ketika tanggal akad melebihi tanggal realisasi</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>Terdapat data Draft Akseptasi yang telah sukses disubmit dan tercatat di database.</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST  {{TESTING_API_GATEWAY}}/akseptasi/loan/inquiry
@@ -2122,71 +2122,72 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-095136-HNGUKI
-ktp: 4288329925398444
-nomor_loan: LN-952100
-</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153345-VAUMAY
+ktp: 7016146106710045
+nomor_loan: LN-514877
+</t>
+        </is>
+      </c>
+      <c r="J25" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L25" s="1" t="n"/>
+      <c r="M25" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N25" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="1" t="inlineStr">
         <is>
           <t>TC-23</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="1" t="inlineStr">
         <is>
           <t>Hit submit draft Akseptasi ketika nomor KTP sdh terdaftar sebelumnya</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">[Test-Step 1] : Buka Postman
 [Test-Step 2] : Set request ke POST {{TESTING_API_GATEWAY}}/akseptasi/draft/submit 
@@ -2194,70 +2195,71 @@
 </t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-095157-JCUEMP
-ktp: 0687495697403336
-</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260929-104922-LFTMVQ
+ktp: 2415980252195211
+</t>
+        </is>
+      </c>
+      <c r="J26" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="K26" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="L26" s="1" t="n"/>
+      <c r="M26" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N26" s="1" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="1" t="inlineStr">
         <is>
           <t>TC-24</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="1" t="inlineStr">
         <is>
           <t>Submit pengajuan dimana (Tanggal Realisasi - Tanggal Lahir) menghasilkan usia kurang dari batas minimum &gt; 18 tahun</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set POST {base_url}/akseptasi/draft/submit
@@ -2265,70 +2267,71 @@
 4. Hit Send</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-095205-NVROFY
-ktp: 1725458943535859
-</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153345-MSORBF
+ktp: 9035435868200838
+</t>
+        </is>
+      </c>
+      <c r="J27" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L27" s="1" t="n"/>
+      <c r="M27" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N27" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="1" t="inlineStr">
         <is>
           <t>TC-25</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="1" t="inlineStr">
         <is>
           <t>Submit pengajuan dimana kalkulasi (Realisasi - Lahir) menghasilkan usia tepat &gt; 18 tahun</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">[Test_Step-1] : Buka Postman
 [Test_Step-2] : Set request ke POST {base_url}/akseptasi/draft/submit
@@ -2337,70 +2340,71 @@
 </t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-095206-SWUPPG
-ktp: 7933509472397987
-</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153345-PRPKCK
+ktp: 8527521652457225
+</t>
+        </is>
+      </c>
+      <c r="J28" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L28" s="1" t="n"/>
+      <c r="M28" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N28" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="1" t="inlineStr">
         <is>
           <t>TC-26</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="1" t="inlineStr">
         <is>
           <t>Submit pengajuan dimana (Usia Riil saat Realisasi + Tenor) melebihi batas maksimal pengajuan 65 tahun (+ 1 hari)</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">[Test_Step-1] : Buka Postman
 [Test_Step-2] : Set request ke POST {base_url}/akseptasi/draft/submit
@@ -2409,70 +2413,71 @@
 </t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-095206-ELFQJA
-ktp: 8630458139439239
-</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260921-085946-VKUBZV
+ktp: 2604210464176949
+</t>
+        </is>
+      </c>
+      <c r="J29" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="K29" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="L29" s="1" t="n"/>
+      <c r="M29" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N29" s="1" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="1" t="inlineStr">
         <is>
           <t>TC-27</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="1" t="inlineStr">
         <is>
           <t>Submit pengajuan dengan input parameter 'usia' fiktif/salah, namun Tanggal Lahir dan Realisasi menghasilkan usia yang valid  (usia pas 65 tahun)</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="1" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">[Test_Step-1] : Buka Postman
 [Test_Step-2] : Set request ke POST {base_url}/akseptasi/draft/submit
@@ -2481,141 +2486,143 @@
 </t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-095206-NUKGML
-ktp: 4201277434371275
-</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153345-YPAVWP
+ktp: 4305378190243245
+</t>
+        </is>
+      </c>
+      <c r="J30" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L30" s="1" t="n"/>
+      <c r="M30" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N30" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>A8 - End to End Flow</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="1" t="inlineStr">
         <is>
           <t>TC-28</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="1" t="inlineStr">
         <is>
           <t>Validasi End-to-End Generate E-Polis &amp; Cek ACS FMS</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="1" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>Sistem siap untuk memproses pengajuan asuransi dari awal (Submit Draft) hingga penerbitan E-Polis.</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="1" t="inlineStr">
         <is>
           <t>1. Buka halaman ACS &amp; FMS
 2. Cari nomor polis
 3. Verifikasi ketersediaan</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-095206-TMEZHX
-ktp: 6621997483706595
-</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153345-FNTOCI
+ktp: 3247581510091971
+</t>
+        </is>
+      </c>
+      <c r="J31" s="1" t="inlineStr">
         <is>
           <t>1. API berhasil memproses request (HTTP 200 OK).
 2. Field dinamis pada response (seperti nomor_transaksi, premi) ter-generate dengan format valid.
 3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="K31" s="1" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L31" s="1" t="n"/>
+      <c r="M31" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N31" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>A8 - End to End Flow</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="1" t="inlineStr">
         <is>
           <t>TC-29</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
         <is>
           <t>Submit kembali Akseptasi setelah Batal (Data sama, Transaksi Beda)</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="1" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>Ada draft akseptasi yang sudah dibatalkan sebelumnya</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="1" t="inlineStr">
         <is>
           <t>1. Hit Submit Draft (Draft 1)
 2. Hit Inquiry Loan
@@ -2625,501 +2632,514 @@
 6. Hit Inquiry Loan ulang dengan Nomor Loan &amp; PK sama</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[DATA UTAMA]
-KTP: 6038990022059559
-Loan: LN-119324
-PK: 26PK634907
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>nomor_transaksi: AKS-20260929-111407-JWMOIQ
+ktp: 5326045060503101
+nomor_transaksi: AKS-20260929-111408-KLNYWS
+nomor_loan: LN-433279
+nomor_transaksi: AKS-20260929-111408-ORLHEX
+nomor_transaksi: AKS-20260929-111408-AHVXHD
+[DATA UTAMA]
+KTP: 5326045060503101
+Loan: LN-433279
+PK: 26PK195541
 [TXs]
-T1: AKS-20260810-093344-WNXJIW
-T2: AKS-20260810-093344-MTBZSU
-T3: AKS-20260810-093345-IINNGQ
-T4: AKS-20260810-093345-TFZEFS
-</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+T1: AKS-20260929-111407-JWMOIQ
+T2: AKS-20260929-111408-KLNYWS
+T3: AKS-20260929-111408-ORLHEX
+T4: AKS-20260929-111408-AHVXHD</t>
+        </is>
+      </c>
+      <c r="J32" s="1" t="inlineStr">
         <is>
           <t>Sistem mengizinkan reuse data (KTP, Loan, PK) selama pengajuan sebelumnya dibatalkan.</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="K32" s="1" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L32" s="1" t="n"/>
+      <c r="M32" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N32" s="1" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="1" t="inlineStr">
         <is>
           <t>TC-30</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="1" t="inlineStr">
         <is>
           <t>Submit Draft - Tenor panjang (15 thn) usia debitur muda (20 thn)</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="1" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="1" t="inlineStr">
         <is>
           <t>1. Set usia_debitur = 20
 2. Set tenor = 180 bulan
 3. Hit endpoint Submit Draft</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260902-161803-BXXUXZ
-ktp: 4604279465860287
-nomor_loan: LN-976237
-</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153516-KDNWED
+ktp: 0209413326610885
+nomor_loan: LN-362423
+nomor_loan: LN-330841
+</t>
+        </is>
+      </c>
+      <c r="J33" s="1" t="inlineStr">
         <is>
           <t>1. API berhasil memproses request (HTTP 200 OK).
 2. Field dinamis pada response (seperti nomor_transaksi, premi) ter-generate dengan format valid.
 3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
+      <c r="L33" s="1" t="n"/>
+      <c r="M33" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N33" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="1" t="inlineStr">
         <is>
           <t>TC-31</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="1" t="inlineStr">
         <is>
           <t>Submit Draft - Tenor panjang (15 thn) batas akhir usia tepat 65 thn</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="1" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="1" t="inlineStr">
         <is>
           <t>1. Set usia_debitur = 50
 2. Set tenor = 180 bulan
 3. Hit endpoint Submit Draft</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260902-145009-WHOOQD
-ktp: 6447939634195919
-nomor_loan: LN-725452
-</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260929-110409-HMUNZL
+ktp: 8347158403760416
+nomor_loan: LN-252707
+</t>
+        </is>
+      </c>
+      <c r="J34" s="1" t="inlineStr">
         <is>
           <t>1. API berhasil memproses request (HTTP 200 OK).
 2. Field dinamis pada response (seperti nomor_transaksi, premi) ter-generate dengan format valid.
 3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>02/09/2026</t>
+      <c r="L34" s="1" t="n"/>
+      <c r="M34" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N34" s="1" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
+      <c r="A35" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="1" t="inlineStr">
         <is>
           <t>TC-32</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="1" t="inlineStr">
         <is>
           <t>Submit Draft - Tenor 6 thn dengan usia akhir 65 thn lebih sehari</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="1" t="inlineStr">
         <is>
           <t>1. Set tenor = 72 bulan
 2. Set usia akhir asuransi = 65 tahun + 1 hari
 3. Hit endpoint Submit Draft</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-100018-TNTREC
-ktp: 6359327397846375
-</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="I35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153543-NNVDZH
+ktp: 0996632121879012
+</t>
+        </is>
+      </c>
+      <c r="J35" s="1" t="inlineStr">
         <is>
           <t>1. API berhasil memproses request (HTTP 200 OK).
 2. Field dinamis pada response (seperti nomor_transaksi, premi) ter-generate dengan format valid.
-3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
+3. Data tidak terecord atau termutasi di Database.</t>
+        </is>
+      </c>
+      <c r="K35" s="1" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L35" s="1" t="n"/>
+      <c r="M35" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N35" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="1" t="inlineStr">
         <is>
           <t>TC-33</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="1" t="inlineStr">
         <is>
           <t>Submit Draft - Usia 55 thn tenor 15 thn (Usia akhir &gt; 65)</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="1" t="inlineStr">
         <is>
           <t>1. Set usia = 55
 2. Set tenor = 180 bulan
 3. Hit endpoint Submit Draft</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-100019-GSUROR
-ktp: 2999787370638519
-</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="I36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260921-090831-LEFDHN
+ktp: 4252173348408969
+</t>
+        </is>
+      </c>
+      <c r="J36" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" s="1" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L36" s="1" t="n"/>
+      <c r="M36" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N36" s="1" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="1" t="inlineStr">
         <is>
           <t>TC-34</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="1" t="inlineStr">
         <is>
           <t>Submit Draft - Inkosistensi logic tenor (10 thn) vs tgl akhir (5 thn)</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="1" t="inlineStr">
         <is>
           <t>1. Set tenor = 120 bulan
 2. Set tanggal_akhir = realisasi + 5 tahun
 3. Hit endpoint Submit Draft</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-100019-XVOYRS
-ktp: 0136768188684338
-</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="I37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260911-135828-NERRDC
+ktp: 3017642078511659
+</t>
+        </is>
+      </c>
+      <c r="J37" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" s="1" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L37" s="1" t="n"/>
+      <c r="M37" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N37" s="1" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>A2 - Submit Draft Akseptasi</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="1" t="inlineStr">
         <is>
           <t>TC-35</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="1" t="inlineStr">
         <is>
           <t>Submit Draft - Inkosistensi logic tenor (2 thn) vs tgl akhir (10 thn)</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>Layanan Submit Draft (A2) beroperasi normal dan koneksi database stabil.</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="1" t="inlineStr">
         <is>
           <t>1. Set tenor = 24 bulan
 2. Set tanggal_akhir = realisasi + 10 tahun
 3. Hit endpoint Submit Draft</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260810-100019-DGMKFO
-ktp: 8318594002702523
-</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260921-081112-GZHJRX
+ktp: 4373199229457784
+</t>
+        </is>
+      </c>
+      <c r="J38" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="K38" s="1" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L38" s="1" t="n"/>
+      <c r="M38" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N38" s="1" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>A1 - Kalkulasi Premi</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="1" t="inlineStr">
         <is>
           <t>TC-36</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="1" t="inlineStr">
         <is>
           <t>Validasi Kalkulasi Premi dengan tenor &gt; 60 bulan (180 bulan) menggunakan rate maksimal (60 bulan = 0.725) dengan UP 100 Juta</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="1" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr">
         <is>
           <t>Layanan Kalkulasi Premi (A1) beroperasi normal dan database stabil.</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="1" t="inlineStr">
         <is>
           <t>1. Buka Postman
 2. Set request ke POST {{TESTING_API_GATEWAY}}/kalkulator/premi
@@ -3127,422 +3147,428 @@
 4. Hit Send dan periksa respons rate &amp; premi</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ktp: 8217887972843606
-</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="I39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ktp: 7128737236828263
+</t>
+        </is>
+      </c>
+      <c r="J39" s="1" t="inlineStr">
         <is>
           <t>1. API berhasil memproses request (HTTP 200 OK).
 2. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
+      <c r="L39" s="1" t="n"/>
+      <c r="M39" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N39" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>Submit Draft Multi Fasilitas</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="1" t="inlineStr">
         <is>
           <t>TC-37</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="1" t="inlineStr">
         <is>
           <t>Submit Draft Akseptasi Multi Fasilitas Akumulasi &lt;= 500Jt</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="1" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
         <is>
           <t>1. Generate KTP
 2. Submit Draft -&gt; Terbit Polis (UP 50 Juta)
 3. Set Payload Baru</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="1" t="inlineStr">
         <is>
           <t>1. Hit API Submit Draft dengan UP 450 Juta</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260820-155153-PZOEXN
-ktp: 1305984111740260
-</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="I40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260928-140446-ECKWPX
+ktp: 3530339661295140
+</t>
+        </is>
+      </c>
+      <c r="J40" s="1" t="inlineStr">
         <is>
           <t>1. API berhasil memproses request (HTTP 200 OK).
 2. Field dinamis pada response (seperti nomor_transaksi, premi) ter-generate dengan format valid.
 3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
+      <c r="L40" s="1" t="n"/>
+      <c r="M40" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N40" s="1" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>Submit Draft Multi Fasilitas</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="1" t="inlineStr">
         <is>
           <t>TC-38</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="1" t="inlineStr">
         <is>
           <t>Submit Draft Akseptasi Multi Fasilitas Akumulasi &gt; 500Jt</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="1" t="inlineStr">
         <is>
           <t>1. Generate KTP
 2. Submit Draft -&gt; Terbit Polis (UP 50 Juta)
 3. Set Payload Baru</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="1" t="inlineStr">
         <is>
           <t>1. Hit API Submit Draft dengan UP 450 Juta 1 Rupiah</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260820-155401-TABFQH
-ktp: 0928839527027039
-</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="I41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260928-140804-JWOBVO
+ktp: 1550406857357698
+</t>
+        </is>
+      </c>
+      <c r="J41" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request dengan status gagal (400/422) dan mengembalikan pesan error validasi.
 2. Muncul pesan Error Limit CBC Accumulation.
 3. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
+      <c r="K41" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="L41" s="1" t="n"/>
+      <c r="M41" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N41" s="1" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>Kalkulator Multi Fasilitas</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="1" t="inlineStr">
         <is>
           <t>TC-39</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="1" t="inlineStr">
         <is>
           <t>Simulasi Kalkulator Premi Multi Fasilitas Akumulasi &lt;= 500Jt</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="1" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="1" t="inlineStr">
         <is>
           <t>1. Generate KTP
 2. Submit Draft -&gt; Terbit Polis (UP 50 Juta)
 3. Set Payload Baru</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="1" t="inlineStr">
         <is>
           <t>1. Hit API Kalkulator Premi dengan UP 450 Juta</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ktp: 7046120439275291
-</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="I42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ktp: 3595450585289228
+</t>
+        </is>
+      </c>
+      <c r="J42" s="1" t="inlineStr">
         <is>
           <t>1. API berhasil memproses simulasi kalkulasi dengan HTTP 200
 2. Total Akumulasi Valid
 3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
+      <c r="L42" s="1" t="n"/>
+      <c r="M42" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N42" s="1" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>Kalkulator Multi Fasilitas</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="1" t="inlineStr">
         <is>
           <t>TC-40</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="1" t="inlineStr">
         <is>
           <t>Simulasi Kalkulator Premi Multi Fasilitas Akumulasi &gt; 500Jt</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="1" t="inlineStr">
         <is>
           <t>1. Generate KTP
 2. Submit Draft -&gt; Terbit Polis (UP 50 Juta)
 3. Set Payload Baru</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="1" t="inlineStr">
         <is>
           <t>1. Hit API Kalkulator Premi dengan UP 450 Juta 1 Rupiah</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ktp: 4341979488740436
-</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="I43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ktp: 9709816737523388
+</t>
+        </is>
+      </c>
+      <c r="J43" s="1" t="inlineStr">
         <is>
           <t>1. API menolak request (HTTP 422).
 2. Muncul pesan Error Limit CBC Accumulation
 3. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
+      <c r="K43" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="L43" s="1" t="n"/>
+      <c r="M43" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N43" s="1" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>Submit Draft Multi Fasilitas</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="1" t="inlineStr">
         <is>
           <t>TC-41</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="1" t="inlineStr">
         <is>
           <t>Submit Draft Akseptasi Multi Fasilitas (Fasilitas Pertama Tenor 180 Bulan) Akumulasi &lt;= 500Jt</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="1" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
         <is>
           <t>1. Generate KTP
 2. Submit Draft dengan Tenor 180 Bulan -&gt; Terbit Polis (UP 50 Juta)
 3. Set Payload Baru</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="1" t="inlineStr">
         <is>
           <t>1. Hit API Submit Draft dengan UP 450 Juta</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260820-155416-JNUTVO
-ktp: 8777671845561086
-</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="I44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260928-140829-BSSRKJ
+ktp: 6105909423406292
+</t>
+        </is>
+      </c>
+      <c r="J44" s="1" t="inlineStr">
         <is>
           <t>1. API berhasil memproses request (HTTP 200 OK).
 2. Field dinamis pada response (seperti nomor_transaksi, premi) ter-generate dengan format valid.
 3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K44" s="1" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Fathur</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
+      <c r="L44" s="1" t="n"/>
+      <c r="M44" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N44" s="1" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>Submit Draft Multi Fasilitas</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="1" t="inlineStr">
         <is>
           <t>TC-42</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="1" t="inlineStr">
         <is>
           <t>Multi Fasilitas &gt; 2 Pengajuan (Limit Berjenjang berdasar Outstanding)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="1" t="inlineStr">
         <is>
           <t>Simulasi 4 pengajuan berturut-turut pada 1 KTP hingga tahap Inquiry Loan</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="1" t="inlineStr">
         <is>
           <t>1. Pengajuan 1: Submit (UP 300jt) -&gt; Inquiry (Out: 200jt)
 2. Pengajuan 2: Submit (UP 200jt) -&gt; Inquiry (Out: 200jt)
@@ -3551,71 +3577,73 @@
 5. Validasi DB Tabel Limit Akumulasi</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260820-155605-IMZMWW
-ktp: 7908190488617109
-nomor_loan: LN-086688
-nomor_transaksi: AKS-20260820-155605-PYVNNE
-nomor_loan: LN-744052
-nomor_transaksi: AKS-20260820-155606-ZMKZBD
-nomor_loan: LN-009170
-nomor_transaksi: AKS-20260820-155606-LPJWHG
-</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="I45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260928-141044-IKGWOJ
+ktp: 0542158486806537
+nomor_loan: LN-837294
+nomor_transaksi: AKS-20260928-141046-TAUKCX
+nomor_loan: LN-082757
+nomor_transaksi: AKS-20260928-141049-JZWYKG
+nomor_loan: LN-433778
+nomor_transaksi: AKS-20260928-141052-WYOFRB
+</t>
+        </is>
+      </c>
+      <c r="J45" s="1" t="inlineStr">
         <is>
           <t>1. Sistem menolak pengajuan Submit Draft ke-4 karena limit akumulasi (Outstanding lama + UP Baru) &gt; 500 Juta
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
+      <c r="K45" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="L45" s="1" t="n"/>
+      <c r="M45" s="1" t="n"/>
+      <c r="N45" s="1" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>Submit Draft Multi Fasilitas</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="1" t="inlineStr">
         <is>
           <t>TC-43</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="1" t="inlineStr">
         <is>
           <t>Multi Fasilitas &gt; 2 Pengajuan Sampai Payment (Limit Berjenjang berdasar Outstanding)</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="1" t="inlineStr">
         <is>
           <t>Simulasi 4 pengajuan berturut-turut pada 1 KTP hingga tahap Payment</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="1" t="inlineStr">
         <is>
           <t>1. Pengajuan 1: Submit (UP 300jt) -&gt; Inquiry -&gt; Otorisasi -&gt; Payment (Polis Terbit)
 2. Pengajuan 2: Submit (UP 200jt) -&gt; Inquiry -&gt; Otorisasi -&gt; Payment (Polis Terbit)
@@ -3624,71 +3652,73 @@
 5. Validasi DB Tabel Limit Akumulasi &amp; Pengecekan ACS, FMS</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260820-155606-KYTATP
-ktp: 6382463712445182
-nomor_loan: LN-037196
-nomor_transaksi: AKS-20260820-155801-REIUHP
-nomor_loan: LN-577490
-nomor_transaksi: AKS-20260820-155957-DVEWWH
-nomor_loan: LN-674157
-nomor_transaksi: AKS-20260820-160155-MUCZXF
-</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="I46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260929-092327-PDFJYC
+ktp: 5655859588110324
+nomor_loan: LN-605822
+nomor_transaksi: AKS-20260929-092402-PISTTK
+nomor_loan: LN-091203
+nomor_transaksi: AKS-20260929-092410-KMFOLB
+nomor_loan: LN-712572
+nomor_transaksi: AKS-20260929-092422-QSJSAC
+</t>
+        </is>
+      </c>
+      <c r="J46" s="1" t="inlineStr">
         <is>
           <t>1. Sistem menolak pengajuan Submit Draft ke-4 karena limit akumulasi (Outstanding lama + UP Baru) &gt; 500 Juta
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
+      <c r="K46" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="L46" s="1" t="n"/>
+      <c r="M46" s="1" t="n"/>
+      <c r="N46" s="1" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>Submit Draft Multi Fasilitas</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="1" t="inlineStr">
         <is>
           <t>TC-44</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="1" t="inlineStr">
         <is>
           <t>Multi Fasilitas Batal (Reset Kalkulasi)</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="1" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="1" t="inlineStr">
         <is>
           <t>Simulasi pengajuan berturut-turut pada 1 KTP hingga tahap Inquiry Loan, lalu batalkan salah satu, dan ajukan lagi untuk memastikan kalkulasi reset</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="1" t="inlineStr">
         <is>
           <t>1. Pengajuan 1: Submit (UP 300jt) -&gt; Inquiry (Out: 200jt)
 2. Pengajuan 2: Submit (UP 200jt) -&gt; Inquiry (Out: 200jt)
@@ -3698,73 +3728,76 @@
 6. Pengajuan 5: Submit (UP 50jt) -&gt; Ditolak (Limit Akumulasi &gt; 500jt)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260820-160155-CQTSOQ
-ktp: 9777963197043459
-nomor_loan: LN-330350
-nomor_transaksi: AKS-20260820-160155-KRYSMR
-nomor_loan: LN-376753
-nomor_transaksi: AKS-20260820-160156-VVXJZW
-nomor_loan: LN-300776
-nomor_transaksi: AKS-20260820-160156-QYCXYK
-nomor_loan: LN-379387
-nomor_transaksi: AKS-20260820-160156-UFWMIK
-</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="I47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260928-141118-QMKTJU
+ktp: 8459301381747385
+nomor_loan: LN-770236
+nomor_transaksi: AKS-20260928-141120-ZNFAEH
+nomor_loan: LN-218983
+nomor_transaksi: AKS-20260928-141122-IAIZFC
+nomor_loan: LN-851902
+ktp: 2530476963430654
+nomor_transaksi: AKS-20260928-141127-KLRCEC
+nomor_loan: LN-369989
+nomor_transaksi: AKS-20260928-141129-SSABXN
+</t>
+        </is>
+      </c>
+      <c r="J47" s="1" t="inlineStr">
         <is>
           <t>1. Sistem menerima pengajuan setelah ada pembatalan, dan menolak pengajuan terakhir karena limit akumulasi (Outstanding lama + UP Baru) &gt; 500 Juta
 2. Data tidak terecord atau termutasi di Database.</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
+      <c r="K47" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="L47" s="1" t="n"/>
+      <c r="M47" s="1" t="n"/>
+      <c r="N47" s="1" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="1" t="inlineStr">
         <is>
           <t>Akseptasi H2H</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>Submit Draft Multi Fasilitas</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="1" t="inlineStr">
         <is>
           <t>TC-45</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="1" t="inlineStr">
         <is>
           <t>Validasi Response Nilai Akumulasi Limit Multi Fasilitas</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="1" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="1" t="inlineStr">
         <is>
           <t>KTP belum memiliki fasilitas aktif. Hit menggunakan API Automation.</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="1" t="inlineStr">
         <is>
           <t>1. Pengajuan 1: Submit Draft (UP 300 Juta) -&gt; Inquiry Loan (Outstanding 100 Juta)
 2. Pengajuan 2: Submit Draft (UP 100 Juta)
@@ -3772,17 +3805,16 @@
 4. Menampilkan Tabel Validasi Response Nilai Akumulasi</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260820-160156-MWWBUF
-ktp: 9207441215116180
-nomor_loan: LN-875740
-nomor_transaksi: AKS-20260820-160157-THXRWK
-nomor_loan: LN-479646
-</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="I48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260923-141701-NDCCKU
+ktp: 5791287051257669
+nomor_loan: LN-9707626965
+nomor_transaksi: AKS-20260923-141718-UAYXHC
+</t>
+        </is>
+      </c>
+      <c r="J48" s="1" t="inlineStr">
         <is>
           <t>1. Sistem memproses pengajuan 2 dengan sukses.
 2. Field nilai_akumulasi pada response sesuai dengan total akumulasi (Outstanding lama + UP Baru).
@@ -3790,18 +3822,1088 @@
 4. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K48" s="1" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="L48" s="1" t="n"/>
+      <c r="M48" s="1" t="n"/>
+      <c r="N48" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>Restitusi</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>API - Restitusi</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>TC-46</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>Submit Restitusi ditolak karena bukan REFUND</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>Polis Terbit</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="inlineStr">
+        <is>
+          <t>1. Melakukan submit restitusi dengan jenis transaksi selain REFUND.
+2. Memvalidasi respon dari API.</t>
+        </is>
+      </c>
+      <c r="I49" s="1" t="inlineStr">
+        <is>
+          <t>nomor_loan: LN-9743134927</t>
+        </is>
+      </c>
+      <c r="J49" s="1" t="inlineStr">
+        <is>
+          <t>API mengembalikan respon penolakan dengan pesan error bahwa jenis transaksi tidak didukung.</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="L49" s="1" t="inlineStr">
+        <is>
+          <t>1. Response API:
+{
+  "status_code": 422,
+  "error": true,
+  "message": "Transaction Type PEMBATALAN SEPIHAK tidak tersedia",
+  "data": null
+}</t>
+        </is>
+      </c>
+      <c r="M49" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N49" s="1" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>Restitusi</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>API - Restitusi</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>TC-47</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>Submit Restitusi gagal jika polis belum lunas</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>Polis Terbit</t>
+        </is>
+      </c>
+      <c r="H50" s="1" t="inlineStr">
+        <is>
+          <t>1. Melakukan submit restitusi menggunakan polis yang status pembayarannya belum lunas.
+2. Memvalidasi respon dari API.</t>
+        </is>
+      </c>
+      <c r="I50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260921-081112-ANNUII
+ktp: 8254937249117028
+</t>
+        </is>
+      </c>
+      <c r="J50" s="1" t="inlineStr">
+        <is>
+          <t>1. API menolak pengajuan restitusi dengan pesan bahwa polis belum lunas.
+2. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>20/08/2026</t>
+      <c r="L50" s="1" t="inlineStr">
+        <is>
+          <t>1. Response API:
+{
+  "status_code": 422,
+  "error": true,
+  "message": "Restitusi tidak dapat diproses - Akseptasi Belum Lunas",
+  "data": null
+}</t>
+        </is>
+      </c>
+      <c r="M50" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N50" s="1" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>Restitusi</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>API - Restitusi</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>TC-48</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>Submit Restitusi berhasil dan memicu tahapan selanjutnya</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>Polis Terbit</t>
+        </is>
+      </c>
+      <c r="H51" s="1" t="inlineStr">
+        <is>
+          <t>1. Melakukan submit restitusi dengan data valid.
+2. Memvalidasi respon sukses dari API.</t>
+        </is>
+      </c>
+      <c r="I51" s="1" t="inlineStr">
+        <is>
+          <t>nomor_loan: LN-0659652387</t>
+        </is>
+      </c>
+      <c r="J51" s="1" t="inlineStr">
+        <is>
+          <t>API menerima pengajuan restitusi dan status berlanjut ke tahap konfirmasi.</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="L51" s="1" t="inlineStr">
+        <is>
+          <t>1. Response API:
+{
+  "status_code": 200,
+  "error": false,
+  "message": "Successfully",
+  "data": {
+    "jenis_restitusi": "PERLUNASAN DIPERCEPAT",
+    "keterangan": "Pelunasan dipercepat oleh debitur",
+    "nilai_disetujui": "65250.0",
+    "nilai_hitung_asuransi": "65250.00",
+    "nilai_pengajuan": "65250.0",
+    "nomor_loan": "LN-0659652387",
+    "pembayaran": null,
+    "rekening_bank": "BCA",
+    "rekening_nomor": "1934567989",
+    "rekening_pemilik": "KATSUI",
+    "status": "Restitusi Disetujui - Proses Pembayaran",
+    "tanggal_restitusi": null,
+    "transaction_type": "REFUND"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M51" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N51" s="1" t="inlineStr">
+        <is>
+          <t>11/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>Restitusi</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>API - Restitusi</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>TC-49</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>Kalkulasi usia &lt;= 30 Hari (Full Refund)</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>Polis Terbit</t>
+        </is>
+      </c>
+      <c r="H52" s="1" t="inlineStr">
+        <is>
+          <t>1. Melakukan submit restitusi untuk polis dengan usia kurang dari atau sama dengan 30 hari.
+2. Memvalidasi nilai kalkulasi restitusi di database.</t>
+        </is>
+      </c>
+      <c r="I52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153909-NBFDNU
+ktp: 0640951844203473
+</t>
+        </is>
+      </c>
+      <c r="J52" s="1" t="inlineStr">
+        <is>
+          <t>1. Nominal kalkulasi dari backend Askrindo sesuai dengan nilai full refund.
+2. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L52" s="1" t="inlineStr">
+        <is>
+          <t>1. Response API:
+{
+  "status_code": 200,
+  "error": false,
+  "message": "Successfully",
+  "data": {
+    "jenis_restitusi": "PERLUNASAN DIPERCEPAT",
+    "keterangan": "Pelunasan dipercepat oleh debitur",
+    "nilai_disetujui": "65250.0",
+    "nilai_hitung_asuransi": "65250.00",
+    "nilai_pengajuan": "65250.0",
+    "nomor_loan": "LN-2421535247",
+    "pembayaran": null,
+    "rekening_bank": "BCA",
+    "rekening_nomor": "1934567989",
+    "rekening_pemilik": "KATSUI",
+    "status": "Restitusi Disetujui - Proses Pembayaran",
+    "tanggal_restitusi": null,
+    "transaction_type": "REFUND"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M52" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N52" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>Restitusi</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>API - Restitusi</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>TC-50</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>Kalkulasi usia &gt; 30 Hari (Proporsional dipotong akuisisi)</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>Polis Terbit</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="inlineStr">
+        <is>
+          <t>1. Melakukan submit restitusi untuk polis dengan usia lebih dari 30 hari.
+2. Memvalidasi nilai kalkulasi restitusi di database.</t>
+        </is>
+      </c>
+      <c r="I53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153909-TDRJRM
+ktp: 9455918640616086
+</t>
+        </is>
+      </c>
+      <c r="J53" s="1" t="inlineStr">
+        <is>
+          <t>1. Nominal kalkulasi dari backend Askrindo sesuai dengan nilai proporsional setelah dipotong biaya akuisisi.
+2. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L53" s="1" t="inlineStr">
+        <is>
+          <t>1. Response API:
+{
+  "status_code": 200,
+  "error": false,
+  "message": "Successfully",
+  "data": {
+    "jenis_restitusi": "PERLUNASAN DIPERCEPAT",
+    "keterangan": "Pelunasan dipercepat oleh debitur",
+    "nilai_disetujui": "20935.14",
+    "nilai_hitung_asuransi": "20935.14",
+    "nilai_pengajuan": "20935.14",
+    "nomor_loan": "LN-2311960901",
+    "pembayaran": null,
+    "rekening_bank": "BCA",
+    "rekening_nomor": "1934567989",
+    "rekening_pemilik": "KATSUI",
+    "status": "Restitusi Disetujui - Proses Pembayaran",
+    "tanggal_restitusi": null,
+    "transaction_type": "REFUND"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M53" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N53" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>Restitusi</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>API - Restitusi</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr">
+        <is>
+          <t>TC-51</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>submit endtoend restitusi dengan nominal pengajuan sesuai dengan kalkulasi Askrindo</t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>Polis Terbit</t>
+        </is>
+      </c>
+      <c r="H54" s="1" t="inlineStr">
+        <is>
+          <t>1. Melakukan submit restitusi dengan nominal sesuai kalkulasi backend.
+2. Mengirimkan konfirmasi AGREED.
+3. Memvalidasi endorsement di ACS dan Jurnal di FMS.</t>
+        </is>
+      </c>
+      <c r="I54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260921-081113-OMWCAX
+ktp: 4543372977028685
+</t>
+        </is>
+      </c>
+      <c r="J54" s="1" t="inlineStr">
+        <is>
+          <t>1. Pengajuan restitusi langsung disetujui tanpa proses sanggah, endorsement terbentuk, dan jurnal BBK ter-create.
+2. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L54" s="1" t="inlineStr">
+        <is>
+          <t>1. Response API:
+{
+  "status_code": 200,
+  "error": false,
+  "message": "Successfully",
+  "data": {
+    "jenis_restitusi": "PERLUNASAN DIPERCEPAT",
+    "keterangan": "Pelunasan dipercepat oleh debitur",
+    "nilai_disetujui": "65250.0",
+    "nilai_hitung_asuransi": "65250.00",
+    "nilai_pengajuan": "65250.0",
+    "nomor_loan": "LN-4527684995",
+    "pembayaran": null,
+    "rekening_bank": "BCA",
+    "rekening_nomor": "1934567989",
+    "rekening_pemilik": "KATSUI",
+    "status": "Restitusi Disetujui - Proses Pembayaran",
+    "tanggal_restitusi": null,
+    "transaction_type": "REFUND"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M54" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N54" s="1" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>Restitusi</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>API - Restitusi</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>TC-52</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>submit endtoend restitusi dab Mitra mengajukan nilai SANGGAHAN awal</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>Polis Terbit</t>
+        </is>
+      </c>
+      <c r="H55" s="1" t="inlineStr">
+        <is>
+          <t>1. Melakukan submit restitusi.
+2. Mengirimkan konfirmasi berupa DISPUTE (Sanggahan).
+3. Memvalidasi status pengajuan.</t>
+        </is>
+      </c>
+      <c r="I55" s="1" t="inlineStr">
+        <is>
+          <t>nomor_loan: LN-0371451937
+No Jurnal BBK: 00030/BBK-03/09/26</t>
+        </is>
+      </c>
+      <c r="J55" s="1" t="inlineStr">
+        <is>
+          <t>Sistem memproses pengajuan sanggahan dari Mitra.</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L55" s="1" t="inlineStr">
+        <is>
+          <t>1. Response API:
+{
+  "status_code": 200,
+  "error": false,
+  "message": "Successfully",
+  "data": {
+    "jenis_restitusi": "PERLUNASAN DIPERCEPAT",
+    "keterangan": "Nilai yang kami ajukan berdasarkan perhitungan proporsional sisa tenor.",
+    "nilai_disetujui": "20935.14",
+    "nilai_hitung_asuransi": "20935.14",
+    "nilai_pengajuan": "20935.14",
+    "nomor_loan": "LN-0371451937",
+    "pembayaran": null,
+    "rekening_bank": "BCA",
+    "rekening_nomor": "1934567989",
+    "rekening_pemilik": "KATSUI",
+    "status": "Restitusi Disetujui - Proses Pembayaran",
+    "tanggal_restitusi": null,
+    "transaction_type": "REFUND"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M55" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N55" s="1" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>Restitusi</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>API - Restitusi</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>TC-53</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>cek pengajuan sanggah dari mitra jika nilainya &lt;= kalkulasi askrindo (auto-AGREED/nominal disetujui)</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>Polis Terbit</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="inlineStr">
+        <is>
+          <t>1. Melakukan submit restitusi.
+2. Mengirimkan konfirmasi DISPUTE dengan nilai lebih kecil atau sama dengan kalkulasi internal Askrindo.
+3. Memvalidasi status menjadi disetujui otomatis.</t>
+        </is>
+      </c>
+      <c r="I56" s="1" t="inlineStr">
+        <is>
+          <t>nomor_loan: LN-3488561695</t>
+        </is>
+      </c>
+      <c r="J56" s="1" t="inlineStr">
+        <is>
+          <t>Sistem otomatis menyetujui nilai sanggahan karena lebih kecil atau sama dengan kalkulasi.</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L56" s="1" t="inlineStr">
+        <is>
+          <t>1. Response API:
+{
+  "status_code": 200,
+  "error": false,
+  "message": "Successfully",
+  "data": {
+    "jenis_restitusi": "PERLUNASAN DIPERCEPAT",
+    "keterangan": "Pelunasan dipercepat oleh debitur",
+    "nilai_disetujui": "65250.0",
+    "nilai_hitung_asuransi": "65250.00",
+    "nilai_pengajuan": "65250.0",
+    "nomor_loan": "LN-3488561695",
+    "pembayaran": null,
+    "rekening_bank": "BCA",
+    "rekening_nomor": "1934567989",
+    "rekening_pemilik": "KATSUI",
+    "status": "Restitusi Disetujui - Proses Pembayaran",
+    "tanggal_restitusi": null,
+    "transaction_type": "REFUND"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M56" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N56" s="1" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>Restitusi</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>API - Restitusi</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>TC-54</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>Sistem Askrindo auto-COUNTER nilai Mitra</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>Polis Terbit</t>
+        </is>
+      </c>
+      <c r="H57" s="1" t="inlineStr">
+        <is>
+          <t>1. Melakukan submit restitusi.
+2. Mengirimkan konfirmasi DISPUTE dengan nilai lebih besar dari kalkulasi Askrindo.
+3. Memvalidasi respon counter dari sistem.</t>
+        </is>
+      </c>
+      <c r="I57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153909-HEZKJM
+ktp: 6890072605912519
+</t>
+        </is>
+      </c>
+      <c r="J57" s="1" t="inlineStr">
+        <is>
+          <t>1. API berhasil memproses request (HTTP 200 OK).
+2. Field dinamis pada response (seperti nomor_transaksi, premi) ter-generate dengan format valid.
+3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L57" s="1" t="inlineStr">
+        <is>
+          <t>1. Response API:
+{
+  "status_code": 200,
+  "error": false,
+  "message": "Successfully",
+  "data": {
+    "jenis_restitusi": "PERLUNASAN DIPERCEPAT",
+    "keterangan": "Nilai yang kami ajukan berdasarkan perhitungan proporsional sisa tenor.",
+    "nilai_disetujui": "20935.14",
+    "nilai_hitung_asuransi": "20935.14",
+    "nilai_pengajuan": "20935.14",
+    "nomor_loan": "LN-5778164946",
+    "pembayaran": null,
+    "rekening_bank": "BCA",
+    "rekening_nomor": "1934567989",
+    "rekening_pemilik": "KATSUI",
+    "status": "Restitusi Disetujui - Proses Pembayaran",
+    "tanggal_restitusi": null,
+    "transaction_type": "REFUND"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M57" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N57" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>Restitusi</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>API - Restitusi</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>TC-55</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>Inquiry get detail restitusi mengembalikan data valid</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G58" s="1" t="inlineStr">
+        <is>
+          <t>Polis Terbit</t>
+        </is>
+      </c>
+      <c r="H58" s="1" t="inlineStr">
+        <is>
+          <t>1. Melakukan submit restitusi.
+2. Memanggil API inquiry detail restitusi.
+3. Memvalidasi kebenaran data pada respon.</t>
+        </is>
+      </c>
+      <c r="I58" s="1" t="inlineStr">
+        <is>
+          <t>nomor_loan: LN-2188977837</t>
+        </is>
+      </c>
+      <c r="J58" s="1" t="inlineStr">
+        <is>
+          <t>Data detail restitusi berhasil dikembalikan dengan lengkap dan valid.</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L58" s="1" t="inlineStr">
+        <is>
+          <t>1. Response API:
+{
+  "status_code": 200,
+  "error": false,
+  "message": "Successfully",
+  "data": {
+    "jenis_restitusi": "PERLUNASAN DIPERCEPAT",
+    "keterangan": "Pelunasan dipercepat oleh debitur",
+    "nilai_disetujui": "65250.0",
+    "nilai_hitung_asuransi": "65250.00",
+    "nilai_pengajuan": "65250.0",
+    "nomor_loan": "LN-2188977837",
+    "pembayaran": null,
+    "rekening_bank": "BCA",
+    "rekening_nomor": "1934567989",
+    "rekening_pemilik": "KATSUI",
+    "status": "Restitusi Disetujui - Proses Pembayaran",
+    "tanggal_restitusi": null,
+    "transaction_type": "REFUND"
+  }
+}</t>
+        </is>
+      </c>
+      <c r="M58" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N58" s="1" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>Restitusi</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>API - Restitusi</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="inlineStr">
+        <is>
+          <t>TC-56</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>Submit Restitusi dengan nomor loan fiktif</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G59" s="1" t="inlineStr">
+        <is>
+          <t>Polis Terbit</t>
+        </is>
+      </c>
+      <c r="H59" s="1" t="inlineStr">
+        <is>
+          <t>1. Melakukan submit restitusi menggunakan nomor loan yang tidak ada di database.
+2. Memvalidasi respon penolakan dari API.</t>
+        </is>
+      </c>
+      <c r="I59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153909-QZGKBV
+ktp: 2085635869298657
+</t>
+        </is>
+      </c>
+      <c r="J59" s="1" t="inlineStr">
+        <is>
+          <t>1. API menolak pengajuan dengan keterangan nomor loan tidak ditemukan.
+2. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L59" s="1" t="inlineStr">
+        <is>
+          <t>1. Response API:
+{
+  "status_code": 422,
+  "error": true,
+  "message": "Data tidak ditemukan untuk Nomor Loan LN-5250010591XXX",
+  "data": null
+}</t>
+        </is>
+      </c>
+      <c r="M59" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N59" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>Restitusi</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>API - Restitusi</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t>TC-57</t>
+        </is>
+      </c>
+      <c r="E60" s="1" t="inlineStr">
+        <is>
+          <t>Kalkulasi usia &lt;= 30 Hari (Full Refund) dan submit nilai pengajuan &gt; nilai premi</t>
+        </is>
+      </c>
+      <c r="F60" s="1" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G60" s="1" t="inlineStr">
+        <is>
+          <t>Polis Terbit</t>
+        </is>
+      </c>
+      <c r="H60" s="1" t="inlineStr">
+        <is>
+          <t>1. Melakukan submit restitusi untuk polis usia kurang dari atau sama dengan 30 hari.
+2. Mengisi nominal pengajuan lebih besar dari nilai premi yang dibayarkan.
+3. Memvalidasi respon penolakan dari API.</t>
+        </is>
+      </c>
+      <c r="I60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153909-KHZXJP
+ktp: 9226308952931881
+</t>
+        </is>
+      </c>
+      <c r="J60" s="1" t="inlineStr">
+        <is>
+          <t>1. API menolak pengajuan atau mengoreksi nilai karena pengajuan melebihi nilai maksimal premi.
+2. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L60" s="1" t="inlineStr">
+        <is>
+          <t>1. Response API:
+{
+  "status_code": 422,
+  "error": true,
+  "message": "Nilai pengajuan melebihi total premi",
+  "data": null
+}</t>
+        </is>
+      </c>
+      <c r="M60" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N60" s="1" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:N2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/collections/test_script.xlsx
+++ b/collections/test_script.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2790,9 +2790,9 @@
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260929-110409-HMUNZL
-ktp: 8347158403760416
-nomor_loan: LN-252707
+          <t xml:space="preserve">nomor_transaksi: AKS-20261007-082831-THKAYE
+ktp: 2781845484047191
+nomor_loan: LN-249375
 </t>
         </is>
       </c>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
     </row>
@@ -4125,8 +4125,8 @@
       </c>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nomor_transaksi: AKS-20260925-153909-NBFDNU
-ktp: 0640951844203473
+          <t xml:space="preserve">nomor_transaksi: AKS-20261005-100916-MPRAIR
+ktp: 0984266348951664
 </t>
         </is>
       </c>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
     </row>
@@ -4900,6 +4900,640 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>Akseptasi</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>API - Submit Draft Akseptasi</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
+          <t>TC-58</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>Penolakan akseptasi menggunakan data debitur berstatus blacklist di Askrindo</t>
+        </is>
+      </c>
+      <c r="F61" s="1" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G61" s="1" t="inlineStr">
+        <is>
+          <t>Mengambil data NIK debitur blacklist dari DB ACS</t>
+        </is>
+      </c>
+      <c r="H61" s="1" t="inlineStr">
+        <is>
+          <t>1. Hit API Submit Draft Akseptasi menggunakan NIK debitur berstatus blacklist.
+2. Memvalidasi respon API terhadap penolakan.</t>
+        </is>
+      </c>
+      <c r="I61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20261007-133944-PKYKQX
+ktp: 0950074704632002
+</t>
+        </is>
+      </c>
+      <c r="J61" s="1" t="inlineStr">
+        <is>
+          <t>1. API menolak pengajuan akseptasi.
+2. Message: Akseptasi Ditolak, Debitur dalam Status Blacklist Askrindo
+3. Data tidak terecord atau termutasi di Database.</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L61" s="1" t="inlineStr"/>
+      <c r="M61" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N61" s="1" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>Restitusi</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>API - Restitusi Confirmation</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t>TC-59</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>Persetujuan restitusi berdasarkan nilai terkecil dari input konfirmasi (Pengajuan Awal &lt; Kalkulasi)</t>
+        </is>
+      </c>
+      <c r="F62" s="1" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t>Polis Terbit</t>
+        </is>
+      </c>
+      <c r="H62" s="1" t="inlineStr">
+        <is>
+          <t>1. Hit API Submit Restitusi dengan nilai pengajuan lebih kecil dari kalkulasi Askrindo.
+2. Hit API Konfirmasi Restitusi dengan nilai konfirmasi lebih kecil dari nilai pengajuan.
+3. Melakukan Validasi DB pada setiap langkah.</t>
+        </is>
+      </c>
+      <c r="I62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20261007-091506-FMSYRM
+ktp: 0598891781029431
+</t>
+        </is>
+      </c>
+      <c r="J62" s="1" t="inlineStr">
+        <is>
+          <t>1. Sistem mencatat dan menyetujui nilai restitusi berdasarkan input konfirmasi (nilai terkecil).
+2. Data ter-update benar di DB.
+3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L62" s="1" t="inlineStr"/>
+      <c r="M62" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N62" s="1" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>Restitusi</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>API - Restitusi Dispute</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>TC-60</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>Persetujuan restitusi setelah proses sanggahan yang memenuhi kalkulasi Askrindo</t>
+        </is>
+      </c>
+      <c r="F63" s="1" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G63" s="1" t="inlineStr">
+        <is>
+          <t>Polis Terbit</t>
+        </is>
+      </c>
+      <c r="H63" s="1" t="inlineStr">
+        <is>
+          <t>1. Hit API Submit Restitusi dengan nilai pengajuan lebih besar dari kalkulasi (Sanggahan).
+2. Hit API Dispute/Sanggahan dengan menginput nilai &lt;= kalkulasi Askrindo.
+3. Melakukan Validasi DB.</t>
+        </is>
+      </c>
+      <c r="I63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20261007-091507-PFQJMK
+ktp: 0598891781029431
+</t>
+        </is>
+      </c>
+      <c r="J63" s="1" t="inlineStr">
+        <is>
+          <t>1. Sanggahan disetujui otomatis setelah nilai memenuhi batas.
+2. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="L63" s="1" t="inlineStr"/>
+      <c r="M63" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N63" s="1" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>Restitusi</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>API - Restitusi Dispute</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t>TC-61</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t>Penolakan sanggahan restitusi ilegal dengan nilai lebih besar dari pengajuan awal</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G64" s="1" t="inlineStr">
+        <is>
+          <t>Polis Terbit</t>
+        </is>
+      </c>
+      <c r="H64" s="1" t="inlineStr">
+        <is>
+          <t>1. Hit API Submit Restitusi dengan nilai pengajuan awal di bawah batas kalkulasi.
+2. Hit API Sanggahan dengan memasukkan nilai yang lebih besar dari nilai pengajuan awal.
+3. Memvalidasi respon API penolakan.</t>
+        </is>
+      </c>
+      <c r="I64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20261007-091509-TIZTVB
+ktp: 0598891781029431
+</t>
+        </is>
+      </c>
+      <c r="J64" s="1" t="inlineStr">
+        <is>
+          <t>1. API menolak proses sanggahan (HTTP 400).
+2. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="L64" s="1" t="inlineStr"/>
+      <c r="M64" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N64" s="1" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>Restitusi</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>API - Restitusi</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
+          <t>TC-62</t>
+        </is>
+      </c>
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>Pengajuan restitusi berstatus hold untuk premi belum lunas dan dilanjutkan otomatis hingga persetujuan</t>
+        </is>
+      </c>
+      <c r="F65" s="1" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G65" s="1" t="inlineStr">
+        <is>
+          <t>Draft Akseptasi sampai Otorisasi tanpa pelunasan premi</t>
+        </is>
+      </c>
+      <c r="H65" s="1" t="inlineStr">
+        <is>
+          <t>1. Hit API Submit Restitusi saat premi belum lunas.
+2. Validasi status akseptasi di DB menjadi 12 (Hold).
+3. Melakukan patching lunas pada premi di DB ACS.
+4. Menunggu scheduler memperbarui status akseptasi menjadi 13.
+5. Lanjutkan konfirmasi hingga selesai.</t>
+        </is>
+      </c>
+      <c r="I65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20261007-091510-BCKBTI
+ktp: 0598891781029431
+</t>
+        </is>
+      </c>
+      <c r="J65" s="1" t="inlineStr">
+        <is>
+          <t>1. API merespon pengajuan ditahan (Hold).
+2. Status otomatis berubah ke 13 setelah lunas.
+3. Alur konfirmasi berhasil dilakukan.
+4. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="L65" s="1" t="inlineStr"/>
+      <c r="M65" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N65" s="1" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>Akseptasi H2H</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>A8 - Restitusi</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="inlineStr">
+        <is>
+          <t>TC-63</t>
+        </is>
+      </c>
+      <c r="E66" s="1" t="inlineStr">
+        <is>
+          <t>Submit Restitusi dengan Nomor Loan yang sudah memiliki pengajuan restitusi aktif (Double Submit)</t>
+        </is>
+      </c>
+      <c r="F66" s="1" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G66" s="1" t="inlineStr">
+        <is>
+          <t>Terdapat Polis Terbit dan sudah ada pengajuan restitusi yang belum berstatus batal/selesai</t>
+        </is>
+      </c>
+      <c r="H66" s="1" t="inlineStr">
+        <is>
+          <t>1. Hit API Submit Restitusi Pertama (Sukses)
+2. Hit API Submit Restitusi Kedua menggunakan nomor loan yang sama</t>
+        </is>
+      </c>
+      <c r="I66" s="1" t="n"/>
+      <c r="J66" s="1" t="inlineStr">
+        <is>
+          <t>1. Sistem menolak dengan HTTP 422.
+2. Muncul pesan validasi bahwa nomor loan sedang dalam proses restitusi.</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="n"/>
+      <c r="L66" s="1" t="n"/>
+      <c r="M66" s="1" t="n"/>
+      <c r="N66" s="1" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>Restitusi</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>API - Restitusi Confirmation</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="inlineStr">
+        <is>
+          <t>TC-64</t>
+        </is>
+      </c>
+      <c r="E67" s="1" t="inlineStr">
+        <is>
+          <t>Penolakan konfirmasi restitusi ilegal dengan nilai lebih besar dari pengajuan awal</t>
+        </is>
+      </c>
+      <c r="F67" s="1" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G67" s="1" t="inlineStr">
+        <is>
+          <t>Polis Terbit</t>
+        </is>
+      </c>
+      <c r="H67" s="1" t="inlineStr">
+        <is>
+          <t>1. Hit API Submit Restitusi dengan nilai pengajuan awal di bawah batas kalkulasi.
+2. Hit API Konfirmasi (DISETUJUI) dengan memasukkan nilai yang lebih besar dari nilai pengajuan awal.
+3. Memvalidasi respon API penolakan.</t>
+        </is>
+      </c>
+      <c r="I67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20261007-091511-DRWEHX
+ktp: 0598891781029431
+</t>
+        </is>
+      </c>
+      <c r="J67" s="1" t="inlineStr">
+        <is>
+          <t>1. API menolak proses konfirmasi (HTTP 400).
+2. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="L67" s="1" t="inlineStr"/>
+      <c r="M67" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N67" s="1" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>Akseptasi</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>API - Notifikasi Pembayaran</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="inlineStr">
+        <is>
+          <t>TC-65</t>
+        </is>
+      </c>
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t>E2E Akseptasi murni tanpa dilunasi di sistem ACS</t>
+        </is>
+      </c>
+      <c r="F68" s="1" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G68" s="1" t="inlineStr">
+        <is>
+          <t>Polis Terbit di Backend</t>
+        </is>
+      </c>
+      <c r="H68" s="1" t="inlineStr">
+        <is>
+          <t>1. Hit API Submit Draft Akseptasi
+2. Hit API Inquiry Loan
+3. Hit API Otorisasi Penyelia
+4. Hit API Payment
+5. Melakukan DB Validation</t>
+        </is>
+      </c>
+      <c r="I68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20261007-095307-IYGKCR
+ktp: 3682091275928871
+nomor_loan: LN-130619
+</t>
+        </is>
+      </c>
+      <c r="J68" s="1" t="inlineStr">
+        <is>
+          <t>1. API berhasil memproses seluruh request (HTTP 200 OK).
+2. Status akseptasi menjadi 9 di PostgreSQL tanpa dimutasi lunas di ACS.
+3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L68" s="1" t="inlineStr"/>
+      <c r="M68" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N68" s="1" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>Akseptasi</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>API - Submit Draft Akseptasi</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="inlineStr">
+        <is>
+          <t>TC-66</t>
+        </is>
+      </c>
+      <c r="E69" s="1" t="inlineStr">
+        <is>
+          <t>E2E Akseptasi menggunakan data debitur yang telah diputihkan (IS_BLACKLIST = 0)</t>
+        </is>
+      </c>
+      <c r="F69" s="1" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="G69" s="1" t="inlineStr">
+        <is>
+          <t>Pemutihan status blacklist debitur di DB ACS (Patch ke 0)</t>
+        </is>
+      </c>
+      <c r="H69" s="1" t="inlineStr">
+        <is>
+          <t>1. Set IS_BLACKLIST = 0 di ACS
+2. Hit API Submit Draft Akseptasi
+3. Hit API Inquiry Loan
+4. Hit API Otorisasi Penyelia
+5. Hit API Payment
+6. Melakukan DB Validation</t>
+        </is>
+      </c>
+      <c r="I69" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nomor_transaksi: AKS-20261007-094039-BRGNKJ
+ktp: 0950074506770374
+nomor_loan: LN-374331
+</t>
+        </is>
+      </c>
+      <c r="J69" s="1" t="inlineStr">
+        <is>
+          <t>1. API berhasil memproses seluruh request (HTTP 200 OK).
+2. Debitur tidak lagi diblokir dan proses akseptasi berjalan lancar hingga status 9.
+3. Data tersimpan dan termutasi dengan benar di Database PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="L69" s="1" t="inlineStr"/>
+      <c r="M69" s="1" t="inlineStr">
+        <is>
+          <t>Fathur</t>
+        </is>
+      </c>
+      <c r="N69" s="1" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N2"/>
